--- a/exports/people_edited.xlsx
+++ b/exports/people_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chandlermacleod-my.sharepoint.com/personal/011436_peoplebank_com_au/Documents/Code/LeadEngine/exports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8431638-778C-A74D-B0F2-B1D9831EB089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{D8431638-778C-A74D-B0F2-B1D9831EB089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D145729F-20EF-1B43-B3EA-1B937A0C74BD}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{3E99717E-1E47-0042-B5CE-F42A7DE8C466}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19180" xr2:uid="{3E99717E-1E47-0042-B5CE-F42A7DE8C466}"/>
   </bookViews>
   <sheets>
     <sheet name="people copy" sheetId="1" r:id="rId1"/>
@@ -3312,6 +3312,7 @@
     <col min="2" max="2" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.6640625" customWidth="1"/>
     <col min="5" max="5" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="34" customWidth="1"/>
     <col min="8" max="8" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.33203125" customWidth="1"/>
